--- a/school_1/vor_spartac_1_walls.xlsx
+++ b/school_1/vor_spartac_1_walls.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\МирзаяновИИ\Documents\projects\school_1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" activeTab="3"/>
   </bookViews>
@@ -12,7 +17,7 @@
     <sheet name="библиотека" sheetId="3" r:id="rId3"/>
     <sheet name="Библ откосы" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -563,17 +568,17 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -584,6 +589,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -632,7 +640,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -667,7 +675,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2171,11 +2179,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
+      <c r="A4" s="66"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="58"/>
@@ -2217,14 +2225,14 @@
         <v>1</v>
       </c>
       <c r="E7" s="17">
-        <v>29.24</v>
+        <v>23.61</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="62">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="64" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="17" t="s">
@@ -2235,14 +2243,14 @@
       </c>
       <c r="E8" s="17">
         <f>E7*D8</f>
-        <v>52.631999999999998</v>
+        <v>42.497999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="64" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="17" t="s">
@@ -2253,15 +2261,15 @@
       </c>
       <c r="E9" s="17">
         <f>E7*D9</f>
-        <v>4.3859999999999992</v>
+        <v>3.5414999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="58"/>
@@ -2304,14 +2312,14 @@
       </c>
       <c r="E13" s="17">
         <f>E7</f>
-        <v>29.24</v>
+        <v>23.61</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="62">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="64" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="17" t="s">
@@ -2322,14 +2330,14 @@
       </c>
       <c r="E14" s="17">
         <f>E13*D14</f>
-        <v>4.3859999999999992</v>
+        <v>3.5414999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="65" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -2340,15 +2348,15 @@
       </c>
       <c r="E15" s="17">
         <f>E13*D15</f>
-        <v>52.631999999999998</v>
+        <v>42.497999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="64"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="58"/>
@@ -2391,14 +2399,14 @@
       </c>
       <c r="E19" s="17">
         <f>E13</f>
-        <v>29.24</v>
+        <v>23.61</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="62">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="64" t="s">
         <v>57</v>
       </c>
       <c r="C20" s="17" t="s">
@@ -2409,14 +2417,14 @@
       </c>
       <c r="E20" s="17">
         <f>E19*D20</f>
-        <v>4.3859999999999992</v>
+        <v>3.5414999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="65" t="s">
         <v>64</v>
       </c>
       <c r="C21" s="17" t="s">
@@ -2427,7 +2435,7 @@
       </c>
       <c r="E21" s="17">
         <f>E19*D21</f>
-        <v>8.7719999999999985</v>
+        <v>7.0829999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/school_1/vor_spartac_1_walls.xlsx
+++ b/school_1/vor_spartac_1_walls.xlsx
@@ -2175,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="17">
-        <v>9.2799999999999994</v>
+        <v>2.5499999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">

--- a/school_1/vor_spartac_1_walls.xlsx
+++ b/school_1/vor_spartac_1_walls.xlsx
@@ -9,20 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" activeTab="3"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Пример" sheetId="1" r:id="rId1"/>
     <sheet name="Спортзал" sheetId="2" r:id="rId2"/>
     <sheet name="библиотека" sheetId="3" r:id="rId3"/>
     <sheet name="Библ откосы" sheetId="4" r:id="rId4"/>
+    <sheet name="ВОР2FB" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="81">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -204,9 +205,6 @@
     <t>Шпатлевка гипсовая</t>
   </si>
   <si>
-    <t>Окраска поверхностей потолков с предварительной огрунтовкой поверхностей / в 2 слоя</t>
-  </si>
-  <si>
     <t>Ведомость работ и используемых материалов (Окраска)</t>
   </si>
   <si>
@@ -217,6 +215,57 @@
   </si>
   <si>
     <t>Краска водно-дисперсионная RAL 9003 НГ</t>
+  </si>
+  <si>
+    <t>Окраска поверхностей откосов с предварительной огрунтовкой поверхностей / в 2 слоя</t>
+  </si>
+  <si>
+    <t>Краска водно-дисперсионная RAL 7044</t>
+  </si>
+  <si>
+    <t>Окраска стен с предварительной огрунтовкой поверхностей / в 2 слоя</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов (Окраска  файерборда)</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов (Шпаклевка финишная Файерборд)</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов (Шпаклевка базовая Файерборд)</t>
+  </si>
+  <si>
+    <t>м2</t>
+  </si>
+  <si>
+    <t>Плита Кнауф Файерборд_ / 2500х1200х12.5 м</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>пог. м</t>
+  </si>
+  <si>
+    <t>Профиль_/направляющий/50*50*0,40/3м</t>
+  </si>
+  <si>
+    <t>шт</t>
+  </si>
+  <si>
+    <t>Угол пластиковый_/10*15*2,5м</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Зашивка приборов отопления / ГВЛВ / в 1 слой на каркасе (дымозащитное ограждение из Файерборда)</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов (Файерборд)</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / стен / ГКЛ, ПГП / 2мм.</t>
   </si>
 </sst>
 </file>
@@ -226,7 +275,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,13 +320,27 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -385,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -580,6 +643,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2166,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>52</v>
@@ -2216,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>52</v>
@@ -2302,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>52</v>
@@ -2361,7 +2427,7 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="58"/>
       <c r="B17" s="59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="60"/>
       <c r="D17" s="60"/>
@@ -2389,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>52</v>
@@ -2425,7 +2491,7 @@
         <v>56</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>55</v>
@@ -2446,4 +2512,404 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="51" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="G1" s="69"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="69"/>
+    </row>
+    <row r="3" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="62">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="63">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="F3" s="70"/>
+      <c r="G3" s="69"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="63">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17">
+        <v>22</v>
+      </c>
+      <c r="F4" s="70"/>
+      <c r="G4" s="69"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="63">
+        <v>1</v>
+      </c>
+      <c r="E5" s="17">
+        <v>201</v>
+      </c>
+      <c r="F5" s="70"/>
+      <c r="G5" s="69"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E6" s="17">
+        <v>41.183999999999997</v>
+      </c>
+      <c r="F6" s="70"/>
+      <c r="G6" s="69"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="66"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="G7" s="69"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="58"/>
+      <c r="B8" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="G8" s="68"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="68"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="62">
+        <v>1</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="G10" s="68"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="17">
+        <f>E10*D11</f>
+        <v>67.391999999999996</v>
+      </c>
+      <c r="G11" s="68"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="17">
+        <f>E10*D12</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G12" s="68"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="67"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="G13" s="68"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="58"/>
+      <c r="B14" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="G14" s="68"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="68"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="62">
+        <v>1</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="63">
+        <v>1</v>
+      </c>
+      <c r="E16" s="17">
+        <f>E10</f>
+        <v>37.44</v>
+      </c>
+      <c r="G16" s="68"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B17" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E17" s="17">
+        <f>E16*D17</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G17" s="68"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E18" s="17">
+        <f>E16*D18</f>
+        <v>67.391999999999996</v>
+      </c>
+      <c r="G18" s="68"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="66"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="G19" s="68"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="58"/>
+      <c r="B20" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="G20" s="68"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="68"/>
+    </row>
+    <row r="22" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="62">
+        <v>1</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="63">
+        <v>1</v>
+      </c>
+      <c r="E22" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="G22" s="68"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B23" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E23" s="17">
+        <f>E22*D23</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G23" s="68"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E24" s="17">
+        <f>E22*D24</f>
+        <v>11.231999999999999</v>
+      </c>
+      <c r="G24" s="68"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/school_1/vor_spartac_1_walls.xlsx
+++ b/school_1/vor_spartac_1_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" activeTab="4"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Пример" sheetId="1" r:id="rId1"/>
@@ -17,13 +17,15 @@
     <sheet name="библиотека" sheetId="3" r:id="rId3"/>
     <sheet name="Библ откосы" sheetId="4" r:id="rId4"/>
     <sheet name="ВОР2FB" sheetId="5" r:id="rId5"/>
+    <sheet name="1.030 ВОР" sheetId="7" r:id="rId6"/>
+    <sheet name="1.032 ВОР" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="112">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -266,6 +268,100 @@
   </si>
   <si>
     <t>Подготовка поверхности СКБ / стен / ГКЛ, ПГП / 2мм.</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов (Штукатурка)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Оклейка швов сопряжения бетонных и других поверхностей стен, перегородок (газобетон, ПГП, панели АКОТЕК и др.) стеклохолстом</t>
+  </si>
+  <si>
+    <t>Штукатурка гипсовая</t>
+  </si>
+  <si>
+    <t>Лента армирующая ( серпянка)_/150мм</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>Шпатлевка гипсовая_ / белая</t>
+  </si>
+  <si>
+    <t>Уголок малярный</t>
+  </si>
+  <si>
+    <t>Выравнивание стен с предварительной огрунтовкой / по оштукатуренной поверхности / толщ. 2 мм (Шпаклевка финишна)</t>
+  </si>
+  <si>
+    <t>Окраска поверхности стен с предварительной огрунтовкой / в 2 слоя</t>
+  </si>
+  <si>
+    <t>Грунтовка _ /  универсальная глубокого проникновения</t>
+  </si>
+  <si>
+    <t>Краска водно-дисперсионная интерьерная Акриловая, моющаяся Глянцевая, матовая, Г1(КМ1), RAL 9003</t>
+  </si>
+  <si>
+    <t>Смесь цементно-песчаная М100</t>
+  </si>
+  <si>
+    <t>Профиль маячковый_/ПМ10</t>
+  </si>
+  <si>
+    <t>(Штукатурка  по газобетонному блоку и ПГП)</t>
+  </si>
+  <si>
+    <t>Грунтовка водно-дисперсионная глубокого проникновения "Эконом" 10 кг_/</t>
+  </si>
+  <si>
+    <t>Штукатурка потолка сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм</t>
+  </si>
+  <si>
+    <t>Грунтовка БЕТОН-КОНТАКТ</t>
+  </si>
+  <si>
+    <t>Штукатурка стен сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм
+(Штукатурка  по газобетонному блоку и ПГП)</t>
+  </si>
+  <si>
+    <t>Штукатурка цементная, сухая</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / стен / по штукатурке / 2мм</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов (ГВЛ)</t>
+  </si>
+  <si>
+    <t>Штукатурка цементная, сухая, ТАНИЛИТ_/РС15</t>
+  </si>
+  <si>
+    <t>2.1</t>
   </si>
 </sst>
 </file>
@@ -329,7 +425,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,8 +438,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -444,11 +546,293 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -637,15 +1021,139 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2245,11 +2753,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="58"/>
@@ -2331,11 +2839,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="67"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
+      <c r="A10" s="109"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="109"/>
+      <c r="D10" s="109"/>
+      <c r="E10" s="109"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="58"/>
@@ -2418,11 +2926,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="66"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
+      <c r="A16" s="108"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="58"/>
@@ -2531,7 +3039,7 @@
       <c r="C1" s="60"/>
       <c r="D1" s="60"/>
       <c r="E1" s="60"/>
-      <c r="G1" s="69"/>
+      <c r="G1" s="67"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -2549,7 +3057,7 @@
       <c r="E2" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="69"/>
+      <c r="G2" s="67"/>
     </row>
     <row r="3" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="62">
@@ -2567,8 +3075,8 @@
       <c r="E3" s="17">
         <v>37.44</v>
       </c>
-      <c r="F3" s="70"/>
-      <c r="G3" s="69"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="62" t="s">
@@ -2586,8 +3094,8 @@
       <c r="E4" s="17">
         <v>22</v>
       </c>
-      <c r="F4" s="70"/>
-      <c r="G4" s="69"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="62" t="s">
@@ -2605,8 +3113,8 @@
       <c r="E5" s="17">
         <v>201</v>
       </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="69"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="s">
@@ -2624,16 +3132,16 @@
       <c r="E6" s="17">
         <v>41.183999999999997</v>
       </c>
-      <c r="F6" s="70"/>
-      <c r="G6" s="69"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="G7" s="69"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="58"/>
@@ -2643,7 +3151,7 @@
       <c r="C8" s="60"/>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
-      <c r="G8" s="68"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
@@ -2661,7 +3169,7 @@
       <c r="E9" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="68"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
@@ -2679,7 +3187,7 @@
       <c r="E10" s="17">
         <v>37.44</v>
       </c>
-      <c r="G10" s="68"/>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="62">
@@ -2698,7 +3206,7 @@
         <f>E10*D11</f>
         <v>67.391999999999996</v>
       </c>
-      <c r="G11" s="68"/>
+      <c r="G11" s="66"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="62" t="s">
@@ -2717,15 +3225,15 @@
         <f>E10*D12</f>
         <v>5.6159999999999997</v>
       </c>
-      <c r="G12" s="68"/>
+      <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="67"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="G13" s="68"/>
+      <c r="A13" s="109"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="G13" s="66"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="58"/>
@@ -2735,7 +3243,7 @@
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
       <c r="E14" s="60"/>
-      <c r="G14" s="68"/>
+      <c r="G14" s="66"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
@@ -2753,7 +3261,7 @@
       <c r="E15" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="68"/>
+      <c r="G15" s="66"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="62">
@@ -2772,7 +3280,7 @@
         <f>E10</f>
         <v>37.44</v>
       </c>
-      <c r="G16" s="68"/>
+      <c r="G16" s="66"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="62">
@@ -2791,7 +3299,7 @@
         <f>E16*D17</f>
         <v>5.6159999999999997</v>
       </c>
-      <c r="G17" s="68"/>
+      <c r="G17" s="66"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="62" t="s">
@@ -2810,15 +3318,15 @@
         <f>E16*D18</f>
         <v>67.391999999999996</v>
       </c>
-      <c r="G18" s="68"/>
+      <c r="G18" s="66"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="66"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="G19" s="68"/>
+      <c r="A19" s="108"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
+      <c r="G19" s="66"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="58"/>
@@ -2828,7 +3336,7 @@
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
       <c r="E20" s="60"/>
-      <c r="G20" s="68"/>
+      <c r="G20" s="66"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
@@ -2846,7 +3354,7 @@
       <c r="E21" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="G21" s="68"/>
+      <c r="G21" s="66"/>
     </row>
     <row r="22" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="62">
@@ -2864,7 +3372,7 @@
       <c r="E22" s="17">
         <v>37.44</v>
       </c>
-      <c r="G22" s="68"/>
+      <c r="G22" s="66"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="62">
@@ -2883,7 +3391,7 @@
         <f>E22*D23</f>
         <v>5.6159999999999997</v>
       </c>
-      <c r="G23" s="68"/>
+      <c r="G23" s="66"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="62" t="s">
@@ -2902,7 +3410,7 @@
         <f>E22*D24</f>
         <v>11.231999999999999</v>
       </c>
-      <c r="G24" s="68"/>
+      <c r="G24" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2912,4 +3420,790 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="69"/>
+      <c r="B1" s="107" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="75">
+        <v>1</v>
+      </c>
+      <c r="B3" s="76" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="78">
+        <v>1</v>
+      </c>
+      <c r="E3" s="79"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="112"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="96"/>
+      <c r="B5" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="99"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="90">
+        <v>1</v>
+      </c>
+      <c r="B7" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="93">
+        <v>1</v>
+      </c>
+      <c r="E7" s="94">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8" s="85" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="74">
+        <f>E7*D8</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E9" s="74">
+        <f>D9*E7</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="93">
+        <v>1</v>
+      </c>
+      <c r="E10" s="94" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="88">
+        <v>0.15</v>
+      </c>
+      <c r="E11" s="89" t="e">
+        <f>#REF!*D11</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E12" s="89" t="e">
+        <f>#REF!*D12</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="106">
+        <v>0.3</v>
+      </c>
+      <c r="E13" s="79" t="e">
+        <f>E10*D13</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="112"/>
+      <c r="B14" s="112"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="96"/>
+      <c r="B15" s="97" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="99"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="90">
+        <v>1</v>
+      </c>
+      <c r="B17" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="93">
+        <v>1</v>
+      </c>
+      <c r="E17" s="94">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="88">
+        <v>0.15</v>
+      </c>
+      <c r="E18" s="89">
+        <f>D18*E17</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="95" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="79">
+        <f>D19*E17</f>
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="63">
+        <v>1</v>
+      </c>
+      <c r="E2" s="74">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="63">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="74">
+        <f>D3*E2</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="78">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E4" s="79">
+        <f>D4*E2</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="83">
+        <v>1</v>
+      </c>
+      <c r="E5" s="84">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="63">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="74">
+        <f t="shared" ref="E6" si="0">$E$5*D6</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="89">
+        <f>$E$5*D7*20</f>
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="88">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E8" s="89">
+        <f>$E$5*D8</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="91" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="93">
+        <v>1</v>
+      </c>
+      <c r="E9" s="94">
+        <v>1000</v>
+      </c>
+      <c r="G9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E10" s="74">
+        <f>$E$9*D10</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="74">
+        <f>$E$9*D11*20</f>
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="74">
+        <f>$E$9*D12</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="75" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="78">
+        <v>1</v>
+      </c>
+      <c r="E13" s="79">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="96"/>
+      <c r="B15" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="99"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="90">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="63">
+        <v>1</v>
+      </c>
+      <c r="E17" s="94">
+        <f>E9+E5</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>1.3</v>
+      </c>
+      <c r="E18" s="89">
+        <f>$E$17*D18</f>
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="111" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="79">
+        <f>$E$17*D19</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="96"/>
+      <c r="B21" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="99"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="90">
+        <v>1</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="63">
+        <v>1</v>
+      </c>
+      <c r="E23" s="94">
+        <f>E17</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B24" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E24" s="89">
+        <f>$E$17*D24</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="110" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="78">
+        <v>4.5</v>
+      </c>
+      <c r="E25" s="79">
+        <f>$E$17*D25</f>
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="96"/>
+      <c r="B27" s="97" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="98"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="99"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="90">
+        <v>1</v>
+      </c>
+      <c r="B29" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="93">
+        <v>1</v>
+      </c>
+      <c r="E29" s="94">
+        <f>E23</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="88">
+        <v>0.15</v>
+      </c>
+      <c r="E30" s="89">
+        <f>$E$17*D30</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="104" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E31" s="89">
+        <f>$E$17*D31</f>
+        <v>600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/school_1/vor_spartac_1_walls.xlsx
+++ b/school_1/vor_spartac_1_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" firstSheet="1" activeTab="5"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" firstSheet="5" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Пример" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="114">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -309,15 +309,9 @@
     <t>3.4</t>
   </si>
   <si>
-    <t>Шпатлевка гипсовая_ / белая</t>
-  </si>
-  <si>
     <t>Уголок малярный</t>
   </si>
   <si>
-    <t>Выравнивание стен с предварительной огрунтовкой / по оштукатуренной поверхности / толщ. 2 мм (Шпаклевка финишна)</t>
-  </si>
-  <si>
     <t>Окраска поверхности стен с предварительной огрунтовкой / в 2 слоя</t>
   </si>
   <si>
@@ -333,35 +327,48 @@
     <t>Профиль маячковый_/ПМ10</t>
   </si>
   <si>
-    <t>(Штукатурка  по газобетонному блоку и ПГП)</t>
-  </si>
-  <si>
     <t>Грунтовка водно-дисперсионная глубокого проникновения "Эконом" 10 кг_/</t>
   </si>
   <si>
-    <t>Штукатурка потолка сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм</t>
-  </si>
-  <si>
     <t>Грунтовка БЕТОН-КОНТАКТ</t>
   </si>
   <si>
+    <t>Ведомость работ и используемых материалов (ГВЛ)</t>
+  </si>
+  <si>
+    <t>Штукатурка цементная, сухая, ТАНИЛИТ_/РС15</t>
+  </si>
+  <si>
+    <t>Выравнивание стен с предварительной огрунтовкой / по оштукатуренной поверхности / толщ. 2 мм</t>
+  </si>
+  <si>
+    <t>Шпатлевка цементная</t>
+  </si>
+  <si>
+    <t>Уголок малярный_ / L=3м /25х25 мм</t>
+  </si>
+  <si>
+    <t>Шпатлевка финишная</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / стен / ГКЛ, ПГП / 2мм</t>
+  </si>
+  <si>
+    <t>Штукатурка потолка сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм
+(Штукатурка по ЖБ)</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов (Шпаклевка базовая по ГКЛ)</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов (Шпаклевка финишная по ГКЛ)</t>
+  </si>
+  <si>
     <t>Штукатурка стен сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм
-(Штукатурка  по газобетонному блоку и ПГП)</t>
-  </si>
-  <si>
-    <t>Штукатурка цементная, сухая</t>
-  </si>
-  <si>
-    <t>Подготовка поверхности СКБ / стен / по штукатурке / 2мм</t>
-  </si>
-  <si>
-    <t>Ведомость работ и используемых материалов (ГВЛ)</t>
-  </si>
-  <si>
-    <t>Штукатурка цементная, сухая, ТАНИЛИТ_/РС15</t>
-  </si>
-  <si>
-    <t>2.1</t>
+(Штукатурка по газобетонному блоку и ПГП)</t>
   </si>
 </sst>
 </file>
@@ -425,7 +432,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,12 +447,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -815,24 +828,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1132,28 +1132,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2423,7 +2439,7 @@
       </c>
       <c r="E89" s="32"/>
     </row>
-    <row r="90" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" s="28" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A90" s="25"/>
       <c r="B90" s="15">
         <v>3</v>
@@ -2753,11 +2769,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="108"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="58"/>
@@ -2839,11 +2855,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="109"/>
-      <c r="B10" s="109"/>
-      <c r="C10" s="109"/>
-      <c r="D10" s="109"/>
-      <c r="E10" s="109"/>
+      <c r="A10" s="117"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="58"/>
@@ -2926,11 +2942,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="108"/>
-      <c r="B16" s="108"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
+      <c r="A16" s="116"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="58"/>
@@ -3136,11 +3152,11 @@
       <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
+      <c r="A7" s="116"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
       <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3228,11 +3244,11 @@
       <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="109"/>
-      <c r="B13" s="109"/>
-      <c r="C13" s="109"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
+      <c r="A13" s="117"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
       <c r="G13" s="66"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3321,11 +3337,11 @@
       <c r="G18" s="66"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="108"/>
-      <c r="B19" s="108"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
+      <c r="A19" s="116"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
       <c r="G19" s="66"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3424,7 +3440,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -3436,8 +3452,8 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="69"/>
-      <c r="B1" s="107" t="s">
-        <v>109</v>
+      <c r="B1" s="105" t="s">
+        <v>102</v>
       </c>
       <c r="C1" s="71"/>
       <c r="D1" s="71"/>
@@ -3473,19 +3489,21 @@
       <c r="D3" s="78">
         <v>1</v>
       </c>
-      <c r="E3" s="79"/>
+      <c r="E3" s="79">
+        <v>16.54</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="112"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="96"/>
       <c r="B5" s="97" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="C5" s="98"/>
       <c r="D5" s="98"/>
@@ -3508,7 +3526,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="90">
         <v>1</v>
       </c>
@@ -3522,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="94">
-        <v>1000</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3530,7 +3548,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>55</v>
@@ -3540,10 +3558,10 @@
       </c>
       <c r="E8" s="74">
         <f>E7*D8</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9.9749999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="73" t="s">
         <v>56</v>
       </c>
@@ -3558,165 +3576,372 @@
       </c>
       <c r="E9" s="74">
         <f>D9*E7</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="91" t="s">
+        <v>36.575000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="108"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="109"/>
+      <c r="B11" s="110" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="113" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="114" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="73">
+        <v>1</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="63">
+        <v>1</v>
+      </c>
+      <c r="E13" s="74">
+        <f>E3</f>
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="63">
+        <v>2</v>
+      </c>
+      <c r="E14" s="74">
+        <f>E13*D14</f>
+        <v>33.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E15" s="74">
+        <f>ROUNDDOWN(E13*D15,0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="79">
+        <f>D16*E13</f>
+        <v>2.4809999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="108"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="109"/>
+      <c r="B18" s="110" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="113" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="114" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="73">
+        <v>1</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="63">
+        <v>1</v>
+      </c>
+      <c r="E20" s="74">
+        <f>79.16+E3</f>
+        <v>95.699999999999989</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B21" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E21" s="118">
+        <f>E20*D21</f>
+        <v>14.354999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="63">
+        <v>2</v>
+      </c>
+      <c r="E22" s="74">
+        <f>E20*D22</f>
+        <v>191.39999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="108"/>
+      <c r="B23" s="108"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="108"/>
+      <c r="E23" s="108"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="109"/>
+      <c r="B24" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="112"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="113" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="114" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="73">
+        <v>1</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="63">
+        <v>1</v>
+      </c>
+      <c r="E26" s="74">
+        <v>970.52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B27" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E27" s="74">
+        <f>E26*D27</f>
+        <v>145.578</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="106" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="78">
+        <v>1</v>
+      </c>
+      <c r="E28" s="79">
+        <f>D28*E26</f>
+        <v>970.52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="108"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="96"/>
+      <c r="B30" s="97" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="99"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="90">
+        <v>1</v>
+      </c>
+      <c r="B32" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="93">
+        <v>1</v>
+      </c>
+      <c r="E32" s="94">
+        <f>E20+E26</f>
+        <v>1066.22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B33" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="93">
-        <v>1</v>
-      </c>
-      <c r="E10" s="94" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="86" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="17" t="s">
+      <c r="C33" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="88">
+      <c r="D33" s="88">
         <v>0.15</v>
       </c>
-      <c r="E11" s="89" t="e">
-        <f>#REF!*D11</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="17" t="s">
+      <c r="E33" s="89">
+        <f>D33*E32</f>
+        <v>159.93299999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E12" s="89" t="e">
-        <f>#REF!*D12</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="105" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="106">
+      <c r="D34" s="78">
         <v>0.3</v>
       </c>
-      <c r="E13" s="79" t="e">
-        <f>E10*D13</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="112"/>
-      <c r="B14" s="112"/>
-      <c r="C14" s="112"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="96"/>
-      <c r="B15" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="99"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="100" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="102" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="102" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="103" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="90">
-        <v>1</v>
-      </c>
-      <c r="B17" s="91" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="93">
-        <v>1</v>
-      </c>
-      <c r="E17" s="94">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B18" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="88">
-        <v>0.15</v>
-      </c>
-      <c r="E18" s="89">
-        <f>D18*E17</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="95" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="79">
-        <f>D19*E17</f>
-        <v>300</v>
+      <c r="E34" s="79">
+        <f>D34*E32</f>
+        <v>319.86599999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3726,7 +3951,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -3736,7 +3961,7 @@
     <col min="5" max="5" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="69"/>
       <c r="B1" s="70" t="s">
         <v>81</v>
@@ -3745,7 +3970,7 @@
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="73" t="s">
         <v>82</v>
       </c>
@@ -3759,10 +3984,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="74">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="73" t="s">
         <v>56</v>
       </c>
@@ -3777,10 +4002,10 @@
       </c>
       <c r="E3" s="74">
         <f>D3*E2</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="75" t="s">
         <v>72</v>
       </c>
@@ -3795,15 +4020,15 @@
       </c>
       <c r="E4" s="79">
         <f>D4*E2</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>23.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="80" t="s">
         <v>86</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C5" s="82" t="s">
         <v>52</v>
@@ -3812,15 +4037,15 @@
         <v>1</v>
       </c>
       <c r="E5" s="84">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="73" t="s">
         <v>87</v>
       </c>
       <c r="B6" s="85" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>55</v>
@@ -3829,16 +4054,16 @@
         <v>0.25</v>
       </c>
       <c r="E6" s="74">
-        <f t="shared" ref="E6" si="0">$E$5*D6</f>
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E5*D6</f>
+        <v>7.5425000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="73" t="s">
         <v>88</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C7" s="87" t="s">
         <v>55</v>
@@ -3847,16 +4072,16 @@
         <v>1.8</v>
       </c>
       <c r="E7" s="89">
-        <f>$E$5*D7*20</f>
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E5*D7*20</f>
+        <v>1086.1200000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="73" t="s">
         <v>88</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="87" t="s">
         <v>73</v>
@@ -3865,16 +4090,16 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="E8" s="89">
-        <f>$E$5*D8</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+        <f>E5*D8</f>
+        <v>33.187000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="90" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="91" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C9" s="92" t="s">
         <v>70</v>
@@ -3883,18 +4108,15 @@
         <v>1</v>
       </c>
       <c r="E9" s="94">
-        <v>1000</v>
-      </c>
-      <c r="G9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>104.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="73" t="s">
         <v>90</v>
       </c>
       <c r="B10" s="85" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>73</v>
@@ -3903,16 +4125,16 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="E10" s="74">
-        <f>$E$9*D10</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E9*D10</f>
+        <v>114.851</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="73" t="s">
         <v>91</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>55</v>
@@ -3921,16 +4143,16 @@
         <v>1.8</v>
       </c>
       <c r="E11" s="74">
-        <f>$E$9*D11*20</f>
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <f>E9*D11*20</f>
+        <v>3758.7599999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="73" t="s">
         <v>92</v>
       </c>
       <c r="B12" s="104" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>55</v>
@@ -3939,11 +4161,11 @@
         <v>0.15</v>
       </c>
       <c r="E12" s="74">
-        <f>$E$9*D12</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E9*D12</f>
+        <v>15.661499999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="75" t="s">
         <v>93</v>
       </c>
@@ -3960,247 +4182,316 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="96"/>
-      <c r="B15" s="97" t="s">
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="108"/>
+      <c r="B14" s="108"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="109"/>
+      <c r="B15" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="99"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="100" t="s">
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="108"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="101" t="s">
+      <c r="B16" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="102" t="s">
+      <c r="C16" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="102" t="s">
+      <c r="D16" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="103" t="s">
+      <c r="E16" s="114" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="90">
+      <c r="F16" s="108"/>
+    </row>
+    <row r="17" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="73">
         <v>1</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D17" s="63">
         <v>1</v>
       </c>
-      <c r="E17" s="94">
+      <c r="E17" s="74">
         <f>E9+E5</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F17" s="108"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="73">
         <v>1.1000000000000001</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>55</v>
       </c>
       <c r="D18" s="63">
-        <v>1.3</v>
-      </c>
-      <c r="E18" s="89">
-        <f>$E$17*D18</f>
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="74">
+        <f>E17*D18</f>
+        <v>269.15999999999997</v>
+      </c>
+      <c r="F18" s="108"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="111" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="77" t="s">
+      <c r="B19" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="74">
+        <f>ROUNDDOWN(E17*D19,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F19" s="108"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="78">
+      <c r="D20" s="78">
         <v>0.15</v>
       </c>
-      <c r="E19" s="79">
-        <f>$E$17*D19</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="96"/>
-      <c r="B21" s="97" t="s">
+      <c r="E20" s="79">
+        <f>D20*E17</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F20" s="108"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="115"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="108"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="109"/>
+      <c r="B22" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="99"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="100" t="s">
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="108"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="101" t="s">
+      <c r="B23" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="102" t="s">
+      <c r="C23" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="102" t="s">
+      <c r="D23" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="103" t="s">
+      <c r="E23" s="114" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="90">
-        <v>1</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="17" t="s">
+      <c r="F23" s="108"/>
+    </row>
+    <row r="24" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="73">
+        <v>1</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="63">
+        <v>1</v>
+      </c>
+      <c r="E24" s="74">
+        <f>E17</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F24" s="108"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="74">
+        <f>E24*D25</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F25" s="108"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="74">
+        <f>ROUNDDOWN(E24*D26,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F26" s="108"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="106" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="78">
+        <v>1</v>
+      </c>
+      <c r="E27" s="79">
+        <f>D27*E24</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F27" s="108"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="108"/>
+      <c r="B28" s="108"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="109"/>
+      <c r="B29" s="110" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="111"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="113" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="114" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="73">
+        <v>1</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="63">
-        <v>1</v>
-      </c>
-      <c r="E23" s="94">
-        <f>E17</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="73">
+      <c r="D31" s="63">
+        <v>1</v>
+      </c>
+      <c r="E31" s="74">
+        <f>E24</f>
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B24" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="17" t="s">
+      <c r="B32" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="63">
+      <c r="D32" s="63">
         <v>0.15</v>
       </c>
-      <c r="E24" s="89">
-        <f>$E$17*D24</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="75" t="s">
+      <c r="E32" s="74">
+        <f>D32*E31</f>
+        <v>20.186999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="110" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="77" t="s">
+      <c r="B33" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="78">
-        <v>4.5</v>
-      </c>
-      <c r="E25" s="79">
-        <f>$E$17*D25</f>
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="96"/>
-      <c r="B27" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="98"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="99"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="100" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="102" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="102" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="103" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="90">
-        <v>1</v>
-      </c>
-      <c r="B29" s="91" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="93">
-        <v>1</v>
-      </c>
-      <c r="E29" s="94">
-        <f>E23</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B30" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="88">
-        <v>0.15</v>
-      </c>
-      <c r="E30" s="89">
-        <f>$E$17*D30</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="104" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="63">
+      <c r="D33" s="78">
         <v>0.3</v>
       </c>
-      <c r="E31" s="89">
-        <f>$E$17*D31</f>
-        <v>600</v>
+      <c r="E33" s="79">
+        <f>D33*E31</f>
+        <v>40.373999999999995</v>
       </c>
     </row>
   </sheetData>

--- a/school_1/vor_spartac_1_walls.xlsx
+++ b/school_1/vor_spartac_1_walls.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="122">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -369,6 +369,30 @@
   <si>
     <t>Штукатурка стен сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм
 (Штукатурка по газобетонному блоку и ПГП)</t>
+  </si>
+  <si>
+    <t>Устройство перегородок на металлическом каркасе по системе Knauf / С-115.1 / А2-16</t>
+  </si>
+  <si>
+    <t>Прочие материалы для перегородок из ГКЛ (лента, шпатлевка, грунтовка, шуруп, дюбель и пр.) / двойной каркас / 2 слоя облицовки</t>
+  </si>
+  <si>
+    <t>Профиль направляющий ПН 75х40х0,4мм Сталь оцинкованная</t>
+  </si>
+  <si>
+    <t>Гипсовые строительные плиты_ / влагостойкий / 12,5*1200*2500</t>
+  </si>
+  <si>
+    <t>Профиль_/стоечный/50*50*0,60/3м</t>
+  </si>
+  <si>
+    <t>комплект</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / стен / по штукатурке / 2мм</t>
   </si>
 </sst>
 </file>
@@ -1132,9 +1156,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
@@ -1161,14 +1182,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2439,7 +2463,7 @@
       </c>
       <c r="E89" s="32"/>
     </row>
-    <row r="90" spans="1:6" s="28" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="25"/>
       <c r="B90" s="15">
         <v>3</v>
@@ -3440,7 +3464,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -3451,13 +3475,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="69"/>
-      <c r="B1" s="105" t="s">
+      <c r="A1" s="58"/>
+      <c r="B1" s="118" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="72"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
     </row>
     <row r="2" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -3476,471 +3500,543 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="75">
-        <v>1</v>
-      </c>
-      <c r="B3" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="78">
-        <v>1</v>
-      </c>
-      <c r="E3" s="79">
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="62">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="63">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17">
         <v>16.54</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="108"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="96"/>
-      <c r="B5" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="99"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="100" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="102" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="102" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="103" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
-        <v>1</v>
-      </c>
-      <c r="B7" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="92" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="93">
-        <v>1</v>
-      </c>
-      <c r="E7" s="94">
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B8" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E8" s="74">
-        <f>E7*D8</f>
-        <v>9.9749999999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E9" s="74">
-        <f>D9*E7</f>
-        <v>36.575000000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="108"/>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="109"/>
-      <c r="B11" s="110" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="112"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="113" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="114" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="73">
-        <v>1</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="63">
-        <v>1</v>
-      </c>
-      <c r="E13" s="74">
+    <row r="4" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="63">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17">
         <f>E3</f>
         <v>16.54</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="73">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="63">
+        <v>1.42</v>
+      </c>
+      <c r="E5" s="17">
+        <f>D5*E3*2</f>
+        <v>46.973599999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="63">
+        <v>2.1</v>
+      </c>
+      <c r="E6" s="17">
+        <f>D6*E3</f>
+        <v>34.734000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="63">
+        <v>4.07</v>
+      </c>
+      <c r="E7" s="17">
+        <f>D7*E3</f>
+        <v>67.317800000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="99"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="90">
+        <v>1</v>
+      </c>
+      <c r="B11" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="93">
+        <v>1</v>
+      </c>
+      <c r="E11" s="94">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="B12" s="85" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="74">
+        <f>E11*D12</f>
+        <v>9.9749999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E13" s="74">
+        <f>D13*E11</f>
+        <v>36.575000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="107"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="108"/>
+      <c r="B15" s="109" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="73">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="63">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74">
+        <f>E3</f>
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C18" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D18" s="63">
         <v>2</v>
       </c>
-      <c r="E14" s="74">
-        <f>E13*D14</f>
+      <c r="E18" s="74">
+        <f>E17*D18</f>
         <v>33.08</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="73" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B19" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C19" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D19" s="63">
         <v>0.3</v>
       </c>
-      <c r="E15" s="74">
-        <f>ROUNDDOWN(E13*D15,0)</f>
+      <c r="E19" s="74">
+        <f>ROUNDDOWN(E17*D19,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="75" t="s">
+    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="B20" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="77" t="s">
+      <c r="C20" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="78">
+      <c r="D20" s="78">
         <v>0.15</v>
       </c>
-      <c r="E16" s="79">
-        <f>D16*E13</f>
+      <c r="E20" s="79">
+        <f>D20*E17</f>
         <v>2.4809999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="108"/>
-      <c r="B17" s="108"/>
-      <c r="C17" s="108"/>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="109"/>
-      <c r="B18" s="110" t="s">
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="107"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="108"/>
+      <c r="B22" s="109" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="112"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="113" t="s">
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B23" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="60" t="s">
+      <c r="C23" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="60" t="s">
+      <c r="D23" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="114" t="s">
+      <c r="E23" s="113" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="73">
-        <v>1</v>
-      </c>
-      <c r="B20" s="23" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="73">
+        <v>1</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C24" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="63">
-        <v>1</v>
-      </c>
-      <c r="E20" s="74">
+      <c r="D24" s="63">
+        <v>1</v>
+      </c>
+      <c r="E24" s="74">
         <f>79.16+E3</f>
         <v>95.699999999999989</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="73">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B21" s="64" t="s">
+      <c r="B25" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C25" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="63">
+      <c r="D25" s="63">
         <v>0.15</v>
       </c>
-      <c r="E21" s="118">
-        <f>E20*D21</f>
+      <c r="E25" s="115">
+        <f>E24*D25</f>
         <v>14.354999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="73" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="65" t="s">
+      <c r="B26" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C26" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="63">
+      <c r="D26" s="63">
         <v>2</v>
       </c>
-      <c r="E22" s="74">
-        <f>E20*D22</f>
+      <c r="E26" s="74">
+        <f>E24*D26</f>
         <v>191.39999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="108"/>
-      <c r="B23" s="108"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="108"/>
-      <c r="E23" s="108"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="109"/>
-      <c r="B24" s="110" t="s">
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="107"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="108"/>
+      <c r="B28" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="112"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="113" t="s">
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="111"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="61" t="s">
+      <c r="B29" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="C29" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="60" t="s">
+      <c r="D29" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="114" t="s">
+      <c r="E29" s="113" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="73">
-        <v>1</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="17" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="73">
+        <v>1</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="63">
-        <v>1</v>
-      </c>
-      <c r="E26" s="74">
+      <c r="D30" s="63">
+        <v>1</v>
+      </c>
+      <c r="E30" s="74">
         <v>970.52</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="73">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B27" s="64" t="s">
+      <c r="B31" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C31" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="63">
+      <c r="D31" s="63">
         <v>0.15</v>
       </c>
-      <c r="E27" s="74">
-        <f>E26*D27</f>
+      <c r="E31" s="74">
+        <f>E30*D31</f>
         <v>145.578</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="75" t="s">
+    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="106" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="77" t="s">
+      <c r="B32" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="78">
-        <v>1</v>
-      </c>
-      <c r="E28" s="79">
-        <f>D28*E26</f>
-        <v>970.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="108"/>
-      <c r="B29" s="108"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="108"/>
-      <c r="E29" s="108"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="96"/>
-      <c r="B30" s="97" t="s">
+      <c r="D32" s="78">
+        <v>2</v>
+      </c>
+      <c r="E32" s="79">
+        <f>D32*E30</f>
+        <v>1941.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="107"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="96"/>
+      <c r="B34" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="99"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="100" t="s">
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="99"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="101" t="s">
+      <c r="B35" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="102" t="s">
+      <c r="C35" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="102" t="s">
+      <c r="D35" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="103" t="s">
+      <c r="E35" s="103" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="90">
-        <v>1</v>
-      </c>
-      <c r="B32" s="91" t="s">
+    <row r="36" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="90">
+        <v>1</v>
+      </c>
+      <c r="B36" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="92" t="s">
+      <c r="C36" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="93">
-        <v>1</v>
-      </c>
-      <c r="E32" s="94">
-        <f>E20+E26</f>
+      <c r="D36" s="93">
+        <v>1</v>
+      </c>
+      <c r="E36" s="94">
+        <f>E24+E30</f>
         <v>1066.22</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="73">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B33" s="86" t="s">
+      <c r="B37" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C37" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="88">
+      <c r="D37" s="88">
         <v>0.15</v>
       </c>
-      <c r="E33" s="89">
-        <f>D33*E32</f>
+      <c r="E37" s="89">
+        <f>D37*E36</f>
         <v>159.93299999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="75" t="s">
+    <row r="38" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="95" t="s">
+      <c r="B38" s="95" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C38" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="78">
+      <c r="D38" s="78">
         <v>0.3</v>
       </c>
-      <c r="E34" s="79">
-        <f>D34*E32</f>
+      <c r="E38" s="79">
+        <f>D38*E36</f>
         <v>319.86599999999999</v>
       </c>
     </row>
@@ -4183,25 +4279,25 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="108"/>
-      <c r="B14" s="108"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
+      <c r="A14" s="107"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="109"/>
-      <c r="B15" s="110" t="s">
+      <c r="A15" s="108"/>
+      <c r="B15" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="112"/>
-      <c r="F15" s="108"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="107"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="113" t="s">
+      <c r="A16" s="112" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="61" t="s">
@@ -4213,10 +4309,10 @@
       <c r="D16" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="114" t="s">
+      <c r="E16" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="108"/>
+      <c r="F16" s="107"/>
     </row>
     <row r="17" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="73">
@@ -4235,7 +4331,7 @@
         <f>E9+E5</f>
         <v>134.57999999999998</v>
       </c>
-      <c r="F17" s="108"/>
+      <c r="F17" s="107"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="73">
@@ -4254,7 +4350,7 @@
         <f>E17*D18</f>
         <v>269.15999999999997</v>
       </c>
-      <c r="F18" s="108"/>
+      <c r="F18" s="107"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="73" t="s">
@@ -4273,13 +4369,13 @@
         <f>ROUNDDOWN(E17*D19,0)</f>
         <v>40</v>
       </c>
-      <c r="F19" s="108"/>
+      <c r="F19" s="107"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="107" t="s">
+      <c r="B20" s="106" t="s">
         <v>57</v>
       </c>
       <c r="C20" s="77" t="s">
@@ -4292,28 +4388,28 @@
         <f>D20*E17</f>
         <v>20.186999999999998</v>
       </c>
-      <c r="F20" s="108"/>
+      <c r="F20" s="107"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="115"/>
-      <c r="B21" s="115"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="108"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="107"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="109"/>
-      <c r="B22" s="110" t="s">
+      <c r="A22" s="108"/>
+      <c r="B22" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="112"/>
-      <c r="F22" s="108"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="107"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="113" t="s">
+      <c r="A23" s="112" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="61" t="s">
@@ -4325,10 +4421,10 @@
       <c r="D23" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="114" t="s">
+      <c r="E23" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="108"/>
+      <c r="F23" s="107"/>
     </row>
     <row r="24" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="73">
@@ -4347,7 +4443,7 @@
         <f>E17</f>
         <v>134.57999999999998</v>
       </c>
-      <c r="F24" s="108"/>
+      <c r="F24" s="107"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="73">
@@ -4366,7 +4462,7 @@
         <f>E24*D25</f>
         <v>20.186999999999998</v>
       </c>
-      <c r="F25" s="108"/>
+      <c r="F25" s="107"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="73" t="s">
@@ -4385,13 +4481,13 @@
         <f>ROUNDDOWN(E24*D26,0)</f>
         <v>40</v>
       </c>
-      <c r="F26" s="108"/>
+      <c r="F26" s="107"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="106" t="s">
+      <c r="B27" s="105" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="77" t="s">
@@ -4404,27 +4500,27 @@
         <f>D27*E24</f>
         <v>134.57999999999998</v>
       </c>
-      <c r="F27" s="108"/>
+      <c r="F27" s="107"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="108"/>
-      <c r="B28" s="108"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="108"/>
+      <c r="A28" s="107"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="109"/>
-      <c r="B29" s="110" t="s">
+      <c r="A29" s="108"/>
+      <c r="B29" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="112"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="111"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="113" t="s">
+      <c r="A30" s="112" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="61" t="s">
@@ -4436,7 +4532,7 @@
       <c r="D30" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="114" t="s">
+      <c r="E30" s="113" t="s">
         <v>51</v>
       </c>
     </row>

--- a/school_1/vor_spartac_1_walls.xlsx
+++ b/school_1/vor_spartac_1_walls.xlsx
@@ -9,23 +9,24 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" firstSheet="5" activeTab="5"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105"/>
   </bookViews>
   <sheets>
-    <sheet name="Пример" sheetId="1" r:id="rId1"/>
-    <sheet name="Спортзал" sheetId="2" r:id="rId2"/>
-    <sheet name="библиотека" sheetId="3" r:id="rId3"/>
-    <sheet name="Библ откосы" sheetId="4" r:id="rId4"/>
-    <sheet name="ВОР2FB" sheetId="5" r:id="rId5"/>
-    <sheet name="1.030 ВОР" sheetId="7" r:id="rId6"/>
-    <sheet name="1.032 ВОР" sheetId="6" r:id="rId7"/>
+    <sheet name="Общий" sheetId="8" r:id="rId1"/>
+    <sheet name="Пример" sheetId="1" r:id="rId2"/>
+    <sheet name="Спортзал" sheetId="2" r:id="rId3"/>
+    <sheet name="библиотека" sheetId="3" r:id="rId4"/>
+    <sheet name="Библ откосы" sheetId="4" r:id="rId5"/>
+    <sheet name="ВОР2FB" sheetId="5" r:id="rId6"/>
+    <sheet name="1.030 ВОР" sheetId="7" r:id="rId7"/>
+    <sheet name="1.032 ВОР" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="252">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -393,16 +394,409 @@
   </si>
   <si>
     <t>Подготовка поверхности СКБ / стен / по штукатурке / 2мм</t>
+  </si>
+  <si>
+    <t>Номер п/п</t>
+  </si>
+  <si>
+    <t>Код узла ИСР</t>
+  </si>
+  <si>
+    <t>Наименование затрат</t>
+  </si>
+  <si>
+    <t>Комментарий подрядчика</t>
+  </si>
+  <si>
+    <t>Коэф.расхода</t>
+  </si>
+  <si>
+    <t>Общее кол-во</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1</t>
+  </si>
+  <si>
+    <t>6.3.1.5.2.1</t>
+  </si>
+  <si>
+    <t>Черновые работы по поверхности стен</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.1</t>
+  </si>
+  <si>
+    <t>6.3.1.5.2.1.2.3</t>
+  </si>
+  <si>
+    <t>Штукатурка стен сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм</t>
+  </si>
+  <si>
+    <t>по жб, №1.030 и 2.037</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.1.1</t>
+  </si>
+  <si>
+    <t>Сетка стеклотканевая 200г/м2, ячейка 5х5мм</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.1.2</t>
+  </si>
+  <si>
+    <t>Грунтовка БЕТОН-КОНТАКТ_/</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.1.3</t>
+  </si>
+  <si>
+    <t>20мм</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.1.4</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.2</t>
+  </si>
+  <si>
+    <t>по блоку, №1.030 и 2.037</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.2.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.2.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.2.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.2.4</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.3</t>
+  </si>
+  <si>
+    <t>жб стены. пом. № 2.058</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.3.1</t>
+  </si>
+  <si>
+    <t>Штукатурка гипсовая_ / Унифицированная по ПИК-СТАНДАРТ, 30кг</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.3.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.3.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.4</t>
+  </si>
+  <si>
+    <t>блок пом.№2.058</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.4.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.4.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.4.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.5</t>
+  </si>
+  <si>
+    <t>помещение №1.007,  жб пов-ть</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.5.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.5.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.5.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.5.4</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.6</t>
+  </si>
+  <si>
+    <t>пом. №1.007 - по блоку</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.6.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.6.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.6.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.6.4</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.7</t>
+  </si>
+  <si>
+    <t>№1.007</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.7.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.7.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.7.3</t>
+  </si>
+  <si>
+    <t>20 мм</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.8</t>
+  </si>
+  <si>
+    <t>6.3.1.5.2.1.4.2</t>
+  </si>
+  <si>
+    <t>№1.030 и 2.0037</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.8.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.8.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.8.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.9</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.9.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.9.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.9.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шпатлевка финишная TERRACO HANDYCOAT ALL PURPOSE </t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.10</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.10.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шпатлевка полимерная суперфинишная ЭЛИСИЛК_/белая/ PP37W </t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.10.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.10.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.11</t>
+  </si>
+  <si>
+    <t>пом.-я №2.058</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.11.1</t>
+  </si>
+  <si>
+    <t>Грунтовка водно-дисперсионная глубокого проникновения EXPORT base Маршалл</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.11.2</t>
+  </si>
+  <si>
+    <t>Лента армированная Серпянка 150мм</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.11.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.11.4</t>
+  </si>
+  <si>
+    <t>Шпатлевка гипсовая_ / белая / Унифицированная по ПИК-СТАНДАРТ, 30кг</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.12</t>
+  </si>
+  <si>
+    <t>пом.№2.058</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.12.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.12.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.12.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.12.4</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.13</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.13.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.13.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.13.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.14</t>
+  </si>
+  <si>
+    <t>помещ. №1.007</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.14.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.14.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.14.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.14.4</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.15</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.15.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.15.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.15.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.15.4</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.16</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.16.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.16.2</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.16.3</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.1.16.4</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.2</t>
+  </si>
+  <si>
+    <t>6.3.1.5.2.2</t>
+  </si>
+  <si>
+    <t>Чистовые работы по поверхности стен</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.2.1</t>
+  </si>
+  <si>
+    <t>6.3.1.5.2.2.3.1</t>
+  </si>
+  <si>
+    <t>пом. №1.030 и 2.037 спорт.залы</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.2.1.1</t>
+  </si>
+  <si>
+    <t>1.1.2.1.1.2.2.1.2</t>
+  </si>
+  <si>
+    <t>прим. по проекту Матовая водно-дисперсионная краска для высококачественной отделки Antega Строитель моющаяся, цвет - белый RAL 9003, КМ1</t>
+  </si>
+  <si>
+    <t>Лист гипсоволокнистый ГВЛ 12,5мм Г1</t>
+  </si>
+  <si>
+    <t>1.1.1.1.1.1.1.1.4</t>
+  </si>
+  <si>
+    <t>1.1.1.1.1.1.1.1.3</t>
+  </si>
+  <si>
+    <t>Профиль_/стоечный/75*50*0,40/3м</t>
+  </si>
+  <si>
+    <t>1.1.1.1.1.1.1.1.2</t>
+  </si>
+  <si>
+    <t>Прочие материалы для облицовки стен из ГКЛ (лента, шпатлевка, грунтовка, шуруп, дюбель и пр.)_ / 1 слой ГКЛ / профиль ПН/ПС 75 мм</t>
+  </si>
+  <si>
+    <t>1.1.1.1.1.1.1.1.1</t>
+  </si>
+  <si>
+    <t>Галерея пом. № 2.058 и пом. №1.007
+применительно как Панели перфорированные звукопоглощающие
+САУНДЛАЙН-Акустика НГ , цвет - белый, 600х600 мм</t>
+  </si>
+  <si>
+    <t>Облицовка стен по системе Knauf / С-665 / в 1 слой / А-12</t>
+  </si>
+  <si>
+    <t>6.2.2.4.2.4.2.9</t>
+  </si>
+  <si>
+    <t>1.1.1.1.1.1.1.1</t>
+  </si>
+  <si>
+    <t>Устройство перегородок и зашивка коммуникаций ГКЛ</t>
+  </si>
+  <si>
+    <t>6.2.2.4.2.4</t>
+  </si>
+  <si>
+    <t>1.1.1.1.1.1.1</t>
+  </si>
+  <si>
+    <t>1. Встроенное и Встроенно-пристроенное СКБ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,8 +849,45 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF800000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,8 +912,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -852,11 +1295,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1185,14 +1693,65 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1498,6 +2057,1748 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I86"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="56.5703125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="14"/>
+    <col min="6" max="6" width="9.28515625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="15" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="126" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="126" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="126" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="126" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="126" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="126" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="126" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="130" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="117" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="117" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="127" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+    </row>
+    <row r="4" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="117" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="117" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="124" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="120" t="s">
+        <v>244</v>
+      </c>
+      <c r="E4" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="123">
+        <v>1</v>
+      </c>
+      <c r="G4" s="123">
+        <v>534.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="117" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="117"/>
+      <c r="C5" s="122" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="120"/>
+      <c r="E5" s="119" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="118">
+        <v>1</v>
+      </c>
+      <c r="G5" s="118">
+        <v>534.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="117"/>
+      <c r="C6" s="122" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="120"/>
+      <c r="E6" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="118">
+        <v>2.1</v>
+      </c>
+      <c r="G6" s="118">
+        <v>1122.24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="117" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="117"/>
+      <c r="C7" s="122" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="120"/>
+      <c r="E7" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="118">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="118">
+        <v>427.52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="117" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" s="117"/>
+      <c r="C8" s="121" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="120"/>
+      <c r="E8" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G8" s="118">
+        <v>587.84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="117" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="127" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="129"/>
+    </row>
+    <row r="10" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="134" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="123">
+        <v>1</v>
+      </c>
+      <c r="G10" s="123">
+        <v>220.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="117"/>
+      <c r="C11" s="122" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="120"/>
+      <c r="E11" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G11" s="118">
+        <v>242.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="117"/>
+      <c r="C12" s="122" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="120"/>
+      <c r="E12" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="118">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="118">
+        <v>55.024999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="117" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="117"/>
+      <c r="C13" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G13" s="125">
+        <v>7923.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="117" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="117"/>
+      <c r="C14" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="120"/>
+      <c r="E14" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G14" s="125">
+        <v>242.11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="134" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="123">
+        <v>1</v>
+      </c>
+      <c r="G15" s="123">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="117"/>
+      <c r="C16" s="122" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="120"/>
+      <c r="E16" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G16" s="118">
+        <v>80.099999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="117"/>
+      <c r="C17" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="120"/>
+      <c r="E17" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G17" s="125">
+        <v>587.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="117" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="117"/>
+      <c r="C18" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G18" s="125">
+        <v>19224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="117" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="117"/>
+      <c r="C19" s="122" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="120"/>
+      <c r="E19" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G19" s="118">
+        <v>587.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="117" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="120" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="123">
+        <v>1</v>
+      </c>
+      <c r="G20" s="123">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="117" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="117"/>
+      <c r="C21" s="121" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="118">
+        <v>1</v>
+      </c>
+      <c r="G21" s="125">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="117" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="117"/>
+      <c r="C22" s="122" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="120"/>
+      <c r="E22" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="118">
+        <v>0.25</v>
+      </c>
+      <c r="G22" s="118">
+        <v>13.475</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="117" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="117"/>
+      <c r="C23" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="120"/>
+      <c r="E23" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G23" s="125">
+        <v>59.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="117" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="120" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="123">
+        <v>1</v>
+      </c>
+      <c r="G24" s="123">
+        <v>260.60000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="117" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="117"/>
+      <c r="C25" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" s="120"/>
+      <c r="E25" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G25" s="125">
+        <v>286.66000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="117" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" s="117"/>
+      <c r="C26" s="122" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="120"/>
+      <c r="E26" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G26" s="125">
+        <v>39.090000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="117" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" s="117"/>
+      <c r="C27" s="121" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="118">
+        <v>1</v>
+      </c>
+      <c r="G27" s="125">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="117" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="120" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="123">
+        <v>1</v>
+      </c>
+      <c r="G28" s="123">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="117" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" s="117"/>
+      <c r="C29" s="122" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="120"/>
+      <c r="E29" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G29" s="118">
+        <v>40.369999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="117" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="117"/>
+      <c r="C30" s="122" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="120"/>
+      <c r="E30" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="118">
+        <v>0.25</v>
+      </c>
+      <c r="G30" s="118">
+        <v>9.1750000000000007</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="117" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" s="117"/>
+      <c r="C31" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G31" s="125">
+        <v>1321.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="117" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="117"/>
+      <c r="C32" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="120"/>
+      <c r="E32" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G32" s="125">
+        <v>40.369999999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="117" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="120" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="123">
+        <v>1</v>
+      </c>
+      <c r="G33" s="123">
+        <v>144.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="117" t="s">
+        <v>167</v>
+      </c>
+      <c r="B34" s="117"/>
+      <c r="C34" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G34" s="125">
+        <v>158.84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="117" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="117"/>
+      <c r="C35" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G35" s="125">
+        <v>5198.3999999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="B36" s="117"/>
+      <c r="C36" s="122" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G36" s="125">
+        <v>21.66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="117" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="117"/>
+      <c r="C37" s="122" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="120"/>
+      <c r="E37" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G37" s="118">
+        <v>158.84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="117" t="s">
+        <v>171</v>
+      </c>
+      <c r="B38" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="D38" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="123">
+        <v>1</v>
+      </c>
+      <c r="G38" s="123">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="117" t="s">
+        <v>173</v>
+      </c>
+      <c r="B39" s="117"/>
+      <c r="C39" s="122" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="120"/>
+      <c r="E39" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" s="118">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G39" s="118">
+        <v>42.68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="117" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="117"/>
+      <c r="C40" s="122" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="120"/>
+      <c r="E40" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G40" s="125">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="117" t="s">
+        <v>175</v>
+      </c>
+      <c r="B41" s="117"/>
+      <c r="C41" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="120" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G41" s="125">
+        <v>1396.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A42" s="117" t="s">
+        <v>177</v>
+      </c>
+      <c r="B42" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="123">
+        <v>1</v>
+      </c>
+      <c r="G42" s="123">
+        <v>754.1</v>
+      </c>
+      <c r="H42" s="14">
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="117" t="s">
+        <v>180</v>
+      </c>
+      <c r="B43" s="117"/>
+      <c r="C43" s="122" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="120"/>
+      <c r="E43" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" s="118">
+        <v>2</v>
+      </c>
+      <c r="G43" s="118">
+        <v>1508.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="117" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" s="117"/>
+      <c r="C44" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="120"/>
+      <c r="E44" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G44" s="125">
+        <v>226.23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="117" t="s">
+        <v>182</v>
+      </c>
+      <c r="B45" s="117"/>
+      <c r="C45" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="120"/>
+      <c r="E45" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G45" s="118">
+        <v>113.11499999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="117" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46" s="123">
+        <v>1</v>
+      </c>
+      <c r="G46" s="123">
+        <v>754.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="B47" s="117"/>
+      <c r="C47" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="120"/>
+      <c r="E47" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G47" s="118">
+        <v>113.11499999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="117" t="s">
+        <v>185</v>
+      </c>
+      <c r="B48" s="117"/>
+      <c r="C48" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="120"/>
+      <c r="E48" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F48" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G48" s="125">
+        <v>226.23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="117" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="117"/>
+      <c r="C49" s="122" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" s="120"/>
+      <c r="E49" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="118">
+        <v>1</v>
+      </c>
+      <c r="G49" s="118">
+        <v>754.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="117" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="E50" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" s="123">
+        <v>1</v>
+      </c>
+      <c r="G50" s="123">
+        <v>754.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="117" t="s">
+        <v>189</v>
+      </c>
+      <c r="B51" s="117"/>
+      <c r="C51" s="122" t="s">
+        <v>190</v>
+      </c>
+      <c r="D51" s="120"/>
+      <c r="E51" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G51" s="118">
+        <v>1357.38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="117" t="s">
+        <v>191</v>
+      </c>
+      <c r="B52" s="117"/>
+      <c r="C52" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="120"/>
+      <c r="E52" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G52" s="125">
+        <v>226.23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53" s="117"/>
+      <c r="C53" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="120"/>
+      <c r="E53" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G53" s="118">
+        <v>113.11499999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="117" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="120" t="s">
+        <v>194</v>
+      </c>
+      <c r="E54" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F54" s="123">
+        <v>1</v>
+      </c>
+      <c r="G54" s="123">
+        <v>314.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="117" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" s="117"/>
+      <c r="C55" s="122" t="s">
+        <v>196</v>
+      </c>
+      <c r="D55" s="120"/>
+      <c r="E55" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="118">
+        <v>0.1</v>
+      </c>
+      <c r="G55" s="118">
+        <v>31.45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="117" t="s">
+        <v>197</v>
+      </c>
+      <c r="B56" s="117"/>
+      <c r="C56" s="122" t="s">
+        <v>198</v>
+      </c>
+      <c r="D56" s="120"/>
+      <c r="E56" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="118">
+        <v>1</v>
+      </c>
+      <c r="G56" s="125">
+        <v>314.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="117" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" s="117"/>
+      <c r="C57" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" s="120"/>
+      <c r="E57" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F57" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G57" s="125">
+        <v>94.35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="117" t="s">
+        <v>200</v>
+      </c>
+      <c r="B58" s="117"/>
+      <c r="C58" s="121" t="s">
+        <v>201</v>
+      </c>
+      <c r="D58" s="120"/>
+      <c r="E58" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G58" s="118">
+        <v>566.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A59" s="117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B59" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="120" t="s">
+        <v>203</v>
+      </c>
+      <c r="E59" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F59" s="123">
+        <v>1</v>
+      </c>
+      <c r="G59" s="123">
+        <v>314.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="117" t="s">
+        <v>204</v>
+      </c>
+      <c r="B60" s="117"/>
+      <c r="C60" s="122" t="s">
+        <v>187</v>
+      </c>
+      <c r="D60" s="120"/>
+      <c r="E60" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60" s="118">
+        <v>1</v>
+      </c>
+      <c r="G60" s="118">
+        <v>314.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="117" t="s">
+        <v>205</v>
+      </c>
+      <c r="B61" s="117"/>
+      <c r="C61" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D61" s="120"/>
+      <c r="E61" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F61" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G61" s="125">
+        <v>94.35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="117" t="s">
+        <v>206</v>
+      </c>
+      <c r="B62" s="117"/>
+      <c r="C62" s="122" t="s">
+        <v>198</v>
+      </c>
+      <c r="D62" s="120"/>
+      <c r="E62" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" s="118">
+        <v>1</v>
+      </c>
+      <c r="G62" s="125">
+        <v>314.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="117" t="s">
+        <v>207</v>
+      </c>
+      <c r="B63" s="117"/>
+      <c r="C63" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="120"/>
+      <c r="E63" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G63" s="118">
+        <v>47.174999999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A64" s="117" t="s">
+        <v>208</v>
+      </c>
+      <c r="B64" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D64" s="120" t="s">
+        <v>203</v>
+      </c>
+      <c r="E64" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F64" s="123">
+        <v>1</v>
+      </c>
+      <c r="G64" s="123">
+        <v>314.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="117" t="s">
+        <v>209</v>
+      </c>
+      <c r="B65" s="117"/>
+      <c r="C65" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="120"/>
+      <c r="E65" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F65" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G65" s="118">
+        <v>47.174999999999997</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="117" t="s">
+        <v>210</v>
+      </c>
+      <c r="B66" s="117"/>
+      <c r="C66" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D66" s="120"/>
+      <c r="E66" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G66" s="125">
+        <v>94.35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="117" t="s">
+        <v>211</v>
+      </c>
+      <c r="B67" s="117"/>
+      <c r="C67" s="122" t="s">
+        <v>190</v>
+      </c>
+      <c r="D67" s="120"/>
+      <c r="E67" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F67" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G67" s="118">
+        <v>566.1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="117" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C68" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D68" s="120" t="s">
+        <v>213</v>
+      </c>
+      <c r="E68" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F68" s="123">
+        <v>1</v>
+      </c>
+      <c r="G68" s="123">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="117" t="s">
+        <v>214</v>
+      </c>
+      <c r="B69" s="117"/>
+      <c r="C69" s="122" t="s">
+        <v>105</v>
+      </c>
+      <c r="D69" s="120"/>
+      <c r="E69" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F69" s="118">
+        <v>2</v>
+      </c>
+      <c r="G69" s="118">
+        <v>439.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="117" t="s">
+        <v>215</v>
+      </c>
+      <c r="B70" s="117"/>
+      <c r="C70" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" s="120"/>
+      <c r="E70" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F70" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G70" s="125">
+        <v>65.97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="117" t="s">
+        <v>216</v>
+      </c>
+      <c r="B71" s="117"/>
+      <c r="C71" s="122" t="s">
+        <v>198</v>
+      </c>
+      <c r="D71" s="120"/>
+      <c r="E71" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="118">
+        <v>1</v>
+      </c>
+      <c r="G71" s="125">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="117" t="s">
+        <v>217</v>
+      </c>
+      <c r="B72" s="117"/>
+      <c r="C72" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="D72" s="120"/>
+      <c r="E72" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F72" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G72" s="118">
+        <v>32.984999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A73" s="117" t="s">
+        <v>218</v>
+      </c>
+      <c r="B73" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C73" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D73" s="120" t="s">
+        <v>213</v>
+      </c>
+      <c r="E73" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F73" s="123">
+        <v>1</v>
+      </c>
+      <c r="G73" s="123">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="117" t="s">
+        <v>219</v>
+      </c>
+      <c r="B74" s="117"/>
+      <c r="C74" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="120"/>
+      <c r="E74" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F74" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G74" s="118">
+        <v>32.984999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="117" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" s="117"/>
+      <c r="C75" s="122" t="s">
+        <v>198</v>
+      </c>
+      <c r="D75" s="120"/>
+      <c r="E75" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F75" s="118">
+        <v>1</v>
+      </c>
+      <c r="G75" s="125">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="117" t="s">
+        <v>221</v>
+      </c>
+      <c r="B76" s="117"/>
+      <c r="C76" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="120"/>
+      <c r="E76" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F76" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G76" s="125">
+        <v>65.97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="117" t="s">
+        <v>222</v>
+      </c>
+      <c r="B77" s="117"/>
+      <c r="C77" s="122" t="s">
+        <v>187</v>
+      </c>
+      <c r="D77" s="120"/>
+      <c r="E77" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F77" s="118">
+        <v>1</v>
+      </c>
+      <c r="G77" s="118">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A78" s="117" t="s">
+        <v>223</v>
+      </c>
+      <c r="B78" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D78" s="120" t="s">
+        <v>213</v>
+      </c>
+      <c r="E78" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F78" s="123">
+        <v>1</v>
+      </c>
+      <c r="G78" s="123">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="117" t="s">
+        <v>224</v>
+      </c>
+      <c r="B79" s="117"/>
+      <c r="C79" s="122" t="s">
+        <v>190</v>
+      </c>
+      <c r="D79" s="120"/>
+      <c r="E79" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F79" s="118">
+        <v>1.8</v>
+      </c>
+      <c r="G79" s="118">
+        <v>395.82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="117" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" s="117"/>
+      <c r="C80" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80" s="120"/>
+      <c r="E80" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="F80" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G80" s="125">
+        <v>65.97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" s="117" t="s">
+        <v>226</v>
+      </c>
+      <c r="B81" s="117"/>
+      <c r="C81" s="122" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="120"/>
+      <c r="E81" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="F81" s="118">
+        <v>1</v>
+      </c>
+      <c r="G81" s="125">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" s="117" t="s">
+        <v>227</v>
+      </c>
+      <c r="B82" s="117"/>
+      <c r="C82" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="120"/>
+      <c r="E82" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F82" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G82" s="118">
+        <v>32.984999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" s="117" t="s">
+        <v>228</v>
+      </c>
+      <c r="B83" s="117" t="s">
+        <v>229</v>
+      </c>
+      <c r="C83" s="127" t="s">
+        <v>230</v>
+      </c>
+      <c r="D83" s="128"/>
+      <c r="E83" s="128"/>
+      <c r="F83" s="128"/>
+      <c r="G83" s="129"/>
+    </row>
+    <row r="84" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A84" s="117" t="s">
+        <v>231</v>
+      </c>
+      <c r="B84" s="117" t="s">
+        <v>232</v>
+      </c>
+      <c r="C84" s="124" t="s">
+        <v>95</v>
+      </c>
+      <c r="D84" s="134" t="s">
+        <v>233</v>
+      </c>
+      <c r="E84" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F84" s="123">
+        <v>1</v>
+      </c>
+      <c r="G84" s="135">
+        <v>754.1</v>
+      </c>
+      <c r="H84" s="14">
+        <v>1066.22</v>
+      </c>
+      <c r="I84" s="14">
+        <v>134.58000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" s="117" t="s">
+        <v>234</v>
+      </c>
+      <c r="B85" s="117"/>
+      <c r="C85" s="122" t="s">
+        <v>96</v>
+      </c>
+      <c r="D85" s="120"/>
+      <c r="E85" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" s="118">
+        <v>0.15</v>
+      </c>
+      <c r="G85" s="118">
+        <v>113.11499999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="117" t="s">
+        <v>235</v>
+      </c>
+      <c r="B86" s="117"/>
+      <c r="C86" s="122" t="s">
+        <v>97</v>
+      </c>
+      <c r="D86" s="120" t="s">
+        <v>236</v>
+      </c>
+      <c r="E86" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F86" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="G86" s="118">
+        <v>226.23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1649,7 +3950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:F92"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2509,7 +4810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A15:E33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2740,7 +5041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2793,11 +5094,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="116"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
+      <c r="A4" s="132"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="58"/>
@@ -2879,11 +5180,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="117"/>
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="58"/>
@@ -2966,11 +5267,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="116"/>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="116"/>
+      <c r="A16" s="132"/>
+      <c r="B16" s="132"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="58"/>
@@ -3062,7 +5363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3176,11 +5477,11 @@
       <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="116"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
       <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3268,11 +5569,11 @@
       <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="117"/>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
       <c r="G13" s="66"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3361,11 +5662,11 @@
       <c r="G18" s="66"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
+      <c r="A19" s="132"/>
+      <c r="B19" s="132"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
       <c r="G19" s="66"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3462,7 +5763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3476,7 +5777,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="58"/>
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="116" t="s">
         <v>102</v>
       </c>
       <c r="C1" s="60"/>
@@ -4045,7 +6346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
